--- a/data/mock/taobao_product_202610.xlsx
+++ b/data/mock/taobao_product_202610.xlsx
@@ -470,10 +470,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>114</v>
+        <v>237</v>
       </c>
       <c r="F2" t="n">
-        <v>1030</v>
+        <v>800</v>
       </c>
     </row>
     <row r="3">
@@ -494,14 +494,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>￥79.00</t>
+          <t>￥119.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>389</v>
+        <v>133</v>
       </c>
       <c r="F3" t="n">
-        <v>441</v>
+        <v>768</v>
       </c>
     </row>
     <row r="4">
@@ -526,10 +526,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>207</v>
+        <v>290</v>
       </c>
       <c r="F4" t="n">
-        <v>1838</v>
+        <v>691</v>
       </c>
     </row>
     <row r="5">
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>336</v>
+        <v>231</v>
       </c>
       <c r="F5" t="n">
-        <v>937</v>
+        <v>982</v>
       </c>
     </row>
     <row r="6">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>325</v>
+        <v>382</v>
       </c>
       <c r="F6" t="n">
-        <v>1674</v>
+        <v>926</v>
       </c>
     </row>
     <row r="7">
@@ -606,14 +606,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>￥499.00</t>
+          <t>￥399.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>348</v>
+        <v>438</v>
       </c>
       <c r="F7" t="n">
-        <v>443</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="8">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>152</v>
+        <v>274</v>
       </c>
       <c r="F8" t="n">
-        <v>1245</v>
+        <v>730</v>
       </c>
     </row>
     <row r="9">
@@ -666,10 +666,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>469</v>
+        <v>431</v>
       </c>
       <c r="F9" t="n">
-        <v>1207</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10">
@@ -690,14 +690,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>￥89.00</t>
+          <t>￥129.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>385</v>
+        <v>144</v>
       </c>
       <c r="F10" t="n">
-        <v>651</v>
+        <v>360</v>
       </c>
     </row>
     <row r="11">
@@ -718,14 +718,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>￥259.00</t>
+          <t>￥189.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229</v>
+        <v>87</v>
       </c>
       <c r="F11" t="n">
-        <v>1347</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -746,14 +746,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>￥329.00</t>
+          <t>￥259.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="F12" t="n">
-        <v>388</v>
+        <v>931</v>
       </c>
     </row>
     <row r="13">
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>234</v>
+        <v>132</v>
       </c>
       <c r="F13" t="n">
-        <v>843</v>
+        <v>870</v>
       </c>
     </row>
     <row r="14">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228</v>
+        <v>415</v>
       </c>
       <c r="F14" t="n">
-        <v>1032</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15">
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>382</v>
+        <v>420</v>
       </c>
       <c r="F15" t="n">
-        <v>552</v>
+        <v>670</v>
       </c>
     </row>
     <row r="16">
@@ -862,10 +862,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>385</v>
+        <v>264</v>
       </c>
       <c r="F16" t="n">
-        <v>541</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>467</v>
+        <v>281</v>
       </c>
       <c r="F17" t="n">
-        <v>1347</v>
+        <v>574</v>
       </c>
     </row>
     <row r="18">
@@ -918,10 +918,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>91</v>
+        <v>241</v>
       </c>
       <c r="F18" t="n">
-        <v>1457</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229</v>
+        <v>172</v>
       </c>
       <c r="F19" t="n">
-        <v>757</v>
+        <v>429</v>
       </c>
     </row>
     <row r="20">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F20" t="n">
-        <v>525</v>
+        <v>898</v>
       </c>
     </row>
     <row r="21">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="F21" t="n">
-        <v>1302</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="22">
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>189</v>
+        <v>241</v>
       </c>
       <c r="F22" t="n">
-        <v>1573</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="23">
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>349</v>
+        <v>50</v>
       </c>
       <c r="F23" t="n">
-        <v>1331</v>
+        <v>965</v>
       </c>
     </row>
     <row r="24">
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>392</v>
+        <v>422</v>
       </c>
       <c r="F24" t="n">
-        <v>1652</v>
+        <v>811</v>
       </c>
     </row>
     <row r="25">
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="F25" t="n">
-        <v>1716</v>
+        <v>912</v>
       </c>
     </row>
     <row r="26">
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>498</v>
+        <v>340</v>
       </c>
       <c r="F26" t="n">
-        <v>1485</v>
+        <v>895</v>
       </c>
     </row>
   </sheetData>

--- a/data/mock/taobao_product_202610.xlsx
+++ b/data/mock/taobao_product_202610.xlsx
@@ -470,10 +470,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>237</v>
+        <v>366</v>
       </c>
       <c r="F2" t="n">
-        <v>800</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="3">
@@ -498,10 +498,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>133</v>
+        <v>402</v>
       </c>
       <c r="F3" t="n">
-        <v>768</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="4">
@@ -526,10 +526,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>290</v>
+        <v>461</v>
       </c>
       <c r="F4" t="n">
-        <v>691</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="5">
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>231</v>
+        <v>277</v>
       </c>
       <c r="F5" t="n">
-        <v>982</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="6">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>382</v>
+        <v>78</v>
       </c>
       <c r="F6" t="n">
-        <v>926</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="7">
@@ -610,10 +610,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="F7" t="n">
-        <v>1900</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="8">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>274</v>
+        <v>165</v>
       </c>
       <c r="F8" t="n">
-        <v>730</v>
+        <v>652</v>
       </c>
     </row>
     <row r="9">
@@ -666,10 +666,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>431</v>
+        <v>58</v>
       </c>
       <c r="F9" t="n">
-        <v>376</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="10">
@@ -694,10 +694,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>144</v>
+        <v>187</v>
       </c>
       <c r="F10" t="n">
-        <v>360</v>
+        <v>577</v>
       </c>
     </row>
     <row r="11">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>87</v>
+        <v>425</v>
       </c>
       <c r="F11" t="n">
-        <v>107</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="12">
@@ -750,10 +750,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>342</v>
+        <v>465</v>
       </c>
       <c r="F12" t="n">
-        <v>931</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="13">
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>132</v>
+        <v>425</v>
       </c>
       <c r="F13" t="n">
-        <v>870</v>
+        <v>547</v>
       </c>
     </row>
     <row r="14">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>415</v>
+        <v>442</v>
       </c>
       <c r="F14" t="n">
-        <v>226</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="15">
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>420</v>
+        <v>255</v>
       </c>
       <c r="F15" t="n">
-        <v>670</v>
+        <v>760</v>
       </c>
     </row>
     <row r="16">
@@ -862,10 +862,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>264</v>
+        <v>384</v>
       </c>
       <c r="F16" t="n">
-        <v>196</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="17">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>281</v>
+        <v>143</v>
       </c>
       <c r="F17" t="n">
-        <v>574</v>
+        <v>778</v>
       </c>
     </row>
     <row r="18">
@@ -918,10 +918,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>241</v>
+        <v>163</v>
       </c>
       <c r="F18" t="n">
-        <v>168</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="19">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>172</v>
+        <v>492</v>
       </c>
       <c r="F19" t="n">
-        <v>429</v>
+        <v>220</v>
       </c>
     </row>
     <row r="20">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="F20" t="n">
-        <v>898</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="21">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>149</v>
+        <v>240</v>
       </c>
       <c r="F21" t="n">
-        <v>1716</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="22">
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>241</v>
+        <v>169</v>
       </c>
       <c r="F22" t="n">
-        <v>1600</v>
+        <v>912</v>
       </c>
     </row>
     <row r="23">
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F23" t="n">
-        <v>965</v>
+        <v>341</v>
       </c>
     </row>
     <row r="24">
@@ -1089,7 +1089,7 @@
         <v>422</v>
       </c>
       <c r="F24" t="n">
-        <v>811</v>
+        <v>418</v>
       </c>
     </row>
     <row r="25">
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>71</v>
+        <v>360</v>
       </c>
       <c r="F25" t="n">
-        <v>912</v>
+        <v>381</v>
       </c>
     </row>
     <row r="26">
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>340</v>
+        <v>253</v>
       </c>
       <c r="F26" t="n">
-        <v>895</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
